--- a/data/test/샘플 템플릿.xlsx
+++ b/data/test/샘플 템플릿.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\shopping_mall_team_project\data\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4F325D-0E89-47B1-8080-E59E1D4FBFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6AE004-FB7B-409C-A1A6-6B79A182C338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46EB818A-E62B-42F0-8864-015BDC999ACA}"/>
+    <workbookView xWindow="3720" yWindow="5010" windowWidth="21600" windowHeight="8820" xr2:uid="{46EB818A-E62B-42F0-8864-015BDC999ACA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,51 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
-  <si>
-    <t>노출수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>클릭수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>상품 상세 방문수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>상품 찜 유저수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>장바구니 유저수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>상품주문수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>반품건수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>광고과금액</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>주문금액</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>상품단가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>카테고리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="57">
   <si>
     <t>스커트&gt;롱스커트</t>
   </si>
@@ -207,29 +163,63 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>계절</t>
+    <t>상품ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>여름</t>
+    <t>분석 시즌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카테고리</t>
   </si>
   <si>
     <t>상품명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>체크남방</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>상품 ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>가을</t>
-  </si>
-  <si>
-    <t>봄</t>
+  </si>
+  <si>
+    <t>노출수</t>
+  </si>
+  <si>
+    <t>클릭수</t>
+  </si>
+  <si>
+    <t>상품 상세 방문수</t>
+  </si>
+  <si>
+    <t>상품 찜 유저수</t>
+  </si>
+  <si>
+    <t>장바구니 유저수</t>
+  </si>
+  <si>
+    <t>상품주문수</t>
+  </si>
+  <si>
+    <t>반품건수</t>
+  </si>
+  <si>
+    <t>광고과금액</t>
+  </si>
+  <si>
+    <t>주문금액</t>
+  </si>
+  <si>
+    <t>상품단가</t>
+  </si>
+  <si>
+    <t>판매 사이트</t>
+  </si>
+  <si>
+    <t>[made/휴가룩🌴]에스닉 사선 레이어드 롱 원피스 - 6color</t>
+  </si>
+  <si>
+    <t>지그재그</t>
+  </si>
+  <si>
+    <t>[당일발송/made/쿨링팬츠🧊]에어리움 썸머 라이트 핀턱 밴딩 팬츠 - 4color</t>
+  </si>
+  <si>
+    <t>[숏,롱]아워썸머 텐셀 밴딩 데님팬츠 - 5size</t>
   </si>
 </sst>
 </file>
@@ -240,7 +230,7 @@
     <numFmt numFmtId="5" formatCode="&quot;₩&quot;#,##0;\-&quot;₩&quot;#,##0"/>
     <numFmt numFmtId="176" formatCode="#,##0.0%;\-#,##0.0%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -268,8 +258,16 @@
       <color rgb="FF212121"/>
       <name val="Amazon Ember"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -279,6 +277,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -331,7 +334,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -350,6 +353,21 @@
     </xf>
     <xf numFmtId="37" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -699,186 +717,195 @@
     <col min="13" max="13" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
-      <c r="A1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:20" ht="33">
+      <c r="A1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C1" t="s">
+      <c r="L1" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="M1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D1" t="s">
+      <c r="N1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="115.5">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="C2" s="9">
+        <v>170117352</v>
+      </c>
+      <c r="D2" s="9">
+        <v>314900</v>
+      </c>
+      <c r="E2" s="9">
+        <v>15917</v>
+      </c>
+      <c r="F2" s="9">
+        <v>17189</v>
+      </c>
+      <c r="G2" s="9">
+        <v>1374</v>
+      </c>
+      <c r="H2" s="9">
+        <v>1089</v>
+      </c>
+      <c r="I2" s="9">
+        <v>406</v>
+      </c>
+      <c r="J2" s="9">
+        <v>31</v>
+      </c>
+      <c r="K2" s="10">
+        <v>973608.98799999931</v>
+      </c>
+      <c r="L2" s="9">
+        <v>12098800</v>
+      </c>
+      <c r="M2" s="9">
+        <v>29800</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="P2" s="6"/>
+    </row>
+    <row r="3" spans="1:20" ht="148.5">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="G1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="B3" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="9">
+        <v>169628746</v>
+      </c>
+      <c r="D3" s="9">
+        <v>218403</v>
+      </c>
+      <c r="E3" s="9">
+        <v>9436</v>
+      </c>
+      <c r="F3" s="9">
+        <v>10573</v>
+      </c>
+      <c r="G3" s="9">
+        <v>604</v>
+      </c>
+      <c r="H3" s="9">
+        <v>847</v>
+      </c>
+      <c r="I3" s="9">
+        <v>401</v>
+      </c>
+      <c r="J3" s="9">
+        <v>38</v>
+      </c>
+      <c r="K3" s="10">
+        <v>1032875.2960000002</v>
+      </c>
+      <c r="L3" s="9">
+        <v>12009400</v>
+      </c>
+      <c r="M3" s="9">
+        <v>29949</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="P3" s="6"/>
+    </row>
+    <row r="4" spans="1:20" ht="82.5">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="M1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1255868</v>
-      </c>
-      <c r="E2" s="3">
-        <v>28981</v>
-      </c>
-      <c r="F2" s="3">
-        <v>1587</v>
-      </c>
-      <c r="G2" s="3">
-        <v>1701</v>
-      </c>
-      <c r="H2" s="3">
-        <v>105</v>
-      </c>
-      <c r="I2" s="3">
-        <v>33</v>
-      </c>
-      <c r="J2" s="3">
-        <v>9</v>
-      </c>
-      <c r="K2" s="3">
-        <v>0</v>
-      </c>
-      <c r="L2" s="3">
-        <v>0</v>
-      </c>
-      <c r="M2" s="2">
-        <v>149580</v>
-      </c>
-      <c r="N2" s="5">
-        <v>5000</v>
-      </c>
-      <c r="O2" s="5"/>
-      <c r="P2" s="6"/>
-    </row>
-    <row r="3" spans="1:20">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="3">
-        <v>1255868</v>
-      </c>
-      <c r="E3" s="3">
-        <v>28981</v>
-      </c>
-      <c r="F3" s="3">
-        <v>1587</v>
-      </c>
-      <c r="G3" s="3">
-        <v>1701</v>
-      </c>
-      <c r="H3" s="3">
-        <v>105</v>
-      </c>
-      <c r="I3" s="3">
-        <v>33</v>
-      </c>
-      <c r="J3" s="3">
-        <v>9</v>
-      </c>
-      <c r="K3" s="3">
-        <v>0</v>
-      </c>
-      <c r="L3" s="3">
-        <v>0</v>
-      </c>
-      <c r="M3" s="2">
-        <v>149580</v>
-      </c>
-      <c r="N3" s="5">
-        <v>5000</v>
-      </c>
-      <c r="O3" s="5"/>
-      <c r="P3" s="6"/>
-    </row>
-    <row r="4" spans="1:20">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="B4" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="9">
+        <v>163511953</v>
+      </c>
+      <c r="D4" s="9">
+        <v>179144</v>
+      </c>
+      <c r="E4" s="9">
+        <v>6881</v>
+      </c>
+      <c r="F4" s="9">
+        <v>7492</v>
+      </c>
+      <c r="G4" s="9">
+        <v>436</v>
+      </c>
+      <c r="H4" s="9">
+        <v>716</v>
+      </c>
+      <c r="I4" s="9">
+        <v>291</v>
+      </c>
+      <c r="J4" s="9">
+        <v>23</v>
+      </c>
+      <c r="K4" s="10">
+        <v>654039.18780000007</v>
+      </c>
+      <c r="L4" s="9">
+        <v>9610400</v>
+      </c>
+      <c r="M4" s="9">
+        <v>33025</v>
+      </c>
+      <c r="N4" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="3">
-        <v>1255868</v>
-      </c>
-      <c r="E4" s="3">
-        <v>28981</v>
-      </c>
-      <c r="F4" s="3">
-        <v>1587</v>
-      </c>
-      <c r="G4" s="3">
-        <v>1701</v>
-      </c>
-      <c r="H4" s="3">
-        <v>105</v>
-      </c>
-      <c r="I4" s="3">
-        <v>33</v>
-      </c>
-      <c r="J4" s="3">
-        <v>9</v>
-      </c>
-      <c r="K4" s="3">
-        <v>0</v>
-      </c>
-      <c r="L4" s="3">
-        <v>0</v>
-      </c>
-      <c r="M4" s="2">
-        <v>149580</v>
-      </c>
-      <c r="N4" s="5">
-        <v>5000</v>
-      </c>
-      <c r="O4" s="5"/>
+      <c r="O4" s="5" t="s">
+        <v>37</v>
+      </c>
       <c r="P4" s="6"/>
     </row>
     <row r="16" spans="1:20">
@@ -893,6 +920,11 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="카테고리를 재 입력하세요" promptTitle="카테고리 선택" sqref="A2:A4" xr:uid="{E74A01A8-89A5-40B1-B531-7CE802185264}">
+      <formula1>INDIRECT("Sheet2!$A$1:$A$34")</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -901,13 +933,13 @@
           <x14:formula1>
             <xm:f>Sheet2!$A$1:$A$34</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A1048576</xm:sqref>
+          <xm:sqref>A5:A1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="계절을 입력하세요" promptTitle="계절 입력" xr:uid="{BF84EA57-A2AC-47F2-A430-45875AC4231A}">
           <x14:formula1>
             <xm:f>Sheet2!$C$1:$C$4</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
+          <xm:sqref>B5:B1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -925,184 +957,184 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
